--- a/AAII_Financials/Quarterly/GIPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GIPR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
   <si>
     <t>GIPR</t>
   </si>
@@ -656,152 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43921</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43646</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43555</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1300</v>
+        <v>1800</v>
       </c>
       <c r="E8" s="3">
         <v>1300</v>
       </c>
       <c r="F8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G8" s="3">
         <v>1400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1000</v>
-      </c>
-      <c r="L8" s="3">
-        <v>900</v>
       </c>
       <c r="M8" s="3">
         <v>900</v>
       </c>
       <c r="N8" s="3">
+        <v>900</v>
+      </c>
+      <c r="O8" s="3">
         <v>1700</v>
-      </c>
-      <c r="O8" s="3">
-        <v>300</v>
       </c>
       <c r="P8" s="3">
         <v>300</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
+      <c r="Q8" s="3">
+        <v>300</v>
       </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E9" s="3">
         <v>300</v>
       </c>
       <c r="F9" s="3">
+        <v>300</v>
+      </c>
+      <c r="G9" s="3">
         <v>400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>300</v>
       </c>
       <c r="H9" s="3">
         <v>300</v>
@@ -810,7 +817,7 @@
         <v>300</v>
       </c>
       <c r="J9" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K9" s="3">
         <v>200</v>
@@ -825,24 +832,27 @@
         <v>200</v>
       </c>
       <c r="O9" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P9" s="3">
         <v>0</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
+      <c r="Q9" s="3">
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="E10" s="3">
         <v>1000</v>
@@ -851,43 +861,46 @@
         <v>1000</v>
       </c>
       <c r="G10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H10" s="3">
         <v>1200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>800</v>
-      </c>
-      <c r="L10" s="3">
-        <v>700</v>
       </c>
       <c r="M10" s="3">
         <v>700</v>
       </c>
       <c r="N10" s="3">
+        <v>700</v>
+      </c>
+      <c r="O10" s="3">
         <v>1500</v>
-      </c>
-      <c r="O10" s="3">
-        <v>300</v>
       </c>
       <c r="P10" s="3">
         <v>300</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
+      <c r="Q10" s="3">
+        <v>300</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,8 +919,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -956,8 +970,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,37 +1023,40 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
@@ -1044,8 +1064,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1056,13 +1076,16 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="E15" s="3">
         <v>600</v>
@@ -1077,13 +1100,13 @@
         <v>600</v>
       </c>
       <c r="I15" s="3">
+        <v>600</v>
+      </c>
+      <c r="J15" s="3">
         <v>400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>300</v>
-      </c>
-      <c r="K15" s="3">
-        <v>400</v>
       </c>
       <c r="L15" s="3">
         <v>400</v>
@@ -1092,22 +1115,25 @@
         <v>400</v>
       </c>
       <c r="N15" s="3">
+        <v>400</v>
+      </c>
+      <c r="O15" s="3">
         <v>700</v>
-      </c>
-      <c r="O15" s="3">
-        <v>100</v>
       </c>
       <c r="P15" s="3">
         <v>100</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
+      <c r="Q15" s="3">
+        <v>100</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1149,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2000</v>
+        <v>3100</v>
       </c>
       <c r="E17" s="3">
         <v>2000</v>
       </c>
       <c r="F17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G17" s="3">
         <v>2300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-700</v>
+        <v>-1300</v>
       </c>
       <c r="E18" s="3">
         <v>-700</v>
       </c>
       <c r="F18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,38 +1276,39 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1287,64 +1321,70 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-300</v>
       </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>-400</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>100</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
         <v>-300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-500</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
+      <c r="Q21" s="3">
+        <v>0</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1393,58 +1433,64 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1493,8 +1539,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1592,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1751,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1804,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1857,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,38 +1910,41 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -1887,64 +1957,70 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2069,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43921</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43646</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43555</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2203,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,44 +2224,45 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E41" s="3">
         <v>2100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>900</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2188,8 +2275,11 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2238,19 +2328,22 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>300</v>
+      </c>
+      <c r="E43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>200</v>
-      </c>
-      <c r="F43" s="3">
-        <v>100</v>
       </c>
       <c r="G43" s="3">
         <v>100</v>
@@ -2273,8 +2366,8 @@
       <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
+      <c r="N43" s="3">
+        <v>100</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
@@ -2288,8 +2381,11 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2338,44 +2434,47 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E45" s="3">
         <v>500</v>
       </c>
       <c r="F45" s="3">
+        <v>500</v>
+      </c>
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
-      </c>
-      <c r="J45" s="3">
-        <v>200</v>
       </c>
       <c r="K45" s="3">
         <v>200</v>
       </c>
       <c r="L45" s="3">
+        <v>200</v>
+      </c>
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2388,8 +2487,11 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2438,8 +2540,11 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2488,8 +2593,11 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2503,29 +2611,29 @@
         <v>6200</v>
       </c>
       <c r="G48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="H48" s="3">
         <v>55800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>56200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>56600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>39000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>35000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>35300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2538,44 +2646,47 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E49" s="3">
         <v>51200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>51700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>52300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2500</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2588,8 +2699,11 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2752,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,8 +2805,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2697,19 +2817,19 @@
         <v>400</v>
       </c>
       <c r="E52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F52" s="3">
         <v>300</v>
       </c>
       <c r="G52" s="3">
+        <v>300</v>
+      </c>
+      <c r="H52" s="3">
         <v>400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>200</v>
       </c>
       <c r="J52" s="3">
         <v>200</v>
@@ -2718,14 +2838,14 @@
         <v>200</v>
       </c>
       <c r="L52" s="3">
+        <v>200</v>
+      </c>
+      <c r="M52" s="3">
         <v>600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>500</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2738,8 +2858,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,44 +2911,47 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>110800</v>
+      </c>
+      <c r="E54" s="3">
         <v>62000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>63200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>64200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>63800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>65300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>66600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>53400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>52400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>39000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>39400</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2838,8 +2964,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2987,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,44 +3008,45 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E57" s="3">
         <v>2500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2700</v>
       </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
       <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
         <v>100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>200</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
       </c>
       <c r="L57" s="3">
+        <v>200</v>
+      </c>
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2928,8 +3059,11 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2958,13 +3092,13 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="M58" s="3">
         <v>1100</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
+      <c r="N58" s="3">
+        <v>1100</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
@@ -2978,44 +3112,47 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7500</v>
+        <v>8100</v>
       </c>
       <c r="E59" s="3">
         <v>7500</v>
       </c>
       <c r="F59" s="3">
+        <v>7500</v>
+      </c>
+      <c r="G59" s="3">
         <v>6900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6800</v>
-      </c>
-      <c r="H59" s="3">
-        <v>6900</v>
       </c>
       <c r="I59" s="3">
         <v>6900</v>
       </c>
       <c r="J59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3028,8 +3165,11 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3078,44 +3218,47 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E61" s="3">
         <v>36500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>36600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>35200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>35400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>35500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>35000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>29000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>26800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27300</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3128,8 +3271,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3178,8 +3324,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3377,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3430,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,44 +3483,47 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>54000</v>
+        <v>93000</v>
       </c>
       <c r="E66" s="3">
         <v>54000</v>
       </c>
       <c r="F66" s="3">
+        <v>54000</v>
+      </c>
+      <c r="G66" s="3">
         <v>53500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>51900</v>
-      </c>
-      <c r="H66" s="3">
-        <v>53700</v>
       </c>
       <c r="I66" s="3">
         <v>53700</v>
       </c>
       <c r="J66" s="3">
+        <v>53700</v>
+      </c>
+      <c r="K66" s="3">
         <v>39800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>37700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>37600</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3378,8 +3536,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3559,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3610,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,13 +3663,16 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>11600</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -3548,8 +3716,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,44 +3769,47 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-8600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-4600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2800</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3648,8 +3822,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3875,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3928,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,44 +3981,47 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E76" s="3">
         <v>8100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1900</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3848,8 +4034,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4087,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43921</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43646</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43555</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,13 +4221,14 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="E83" s="3">
         <v>600</v>
@@ -4044,13 +4243,13 @@
         <v>600</v>
       </c>
       <c r="I83" s="3">
+        <v>600</v>
+      </c>
+      <c r="J83" s="3">
         <v>400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>400</v>
       </c>
       <c r="L83" s="3">
         <v>400</v>
@@ -4059,22 +4258,25 @@
         <v>400</v>
       </c>
       <c r="N83" s="3">
+        <v>400</v>
+      </c>
+      <c r="O83" s="3">
         <v>700</v>
-      </c>
-      <c r="O83" s="3">
-        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>100</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4325,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4378,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4431,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4484,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,58 +4537,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>500</v>
+      </c>
+      <c r="E89" s="3">
         <v>300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
       <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
         <v>100</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
       <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
       <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,47 +4613,48 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-33300</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-12800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16700</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4443,8 +4664,11 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4717,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,58 +4770,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>-33100</v>
       </c>
       <c r="E94" s="3">
         <v>-100</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>100</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +4846,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4628,10 +4862,10 @@
         <v>-300</v>
       </c>
       <c r="G96" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H96" s="3">
         <v>-400</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-300</v>
       </c>
       <c r="I96" s="3">
         <v>-300</v>
@@ -4640,7 +4874,7 @@
         <v>-300</v>
       </c>
       <c r="K96" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4663,8 +4897,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4950,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5003,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,58 +5056,64 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>12300</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-200</v>
       </c>
       <c r="M100" s="3">
         <v>-200</v>
       </c>
       <c r="N100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O100" s="3">
         <v>17600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>700</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4913,54 +5162,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13500</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GIPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GIPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
   <si>
     <t>GIPR</t>
   </si>
@@ -656,174 +656,187 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43921</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43646</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43555</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F8" s="3">
         <v>1800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1300</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1500</v>
       </c>
       <c r="I8" s="3">
         <v>1400</v>
       </c>
       <c r="J8" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L8" s="3">
         <v>1200</v>
-      </c>
-      <c r="K8" s="3">
-        <v>900</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1000</v>
       </c>
       <c r="M8" s="3">
         <v>900</v>
       </c>
       <c r="N8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O8" s="3">
         <v>900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q8" s="3">
         <v>1700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>300</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>600</v>
+      </c>
+      <c r="F9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>300</v>
-      </c>
-      <c r="F9" s="3">
-        <v>300</v>
-      </c>
-      <c r="G9" s="3">
-        <v>400</v>
       </c>
       <c r="H9" s="3">
         <v>300</v>
       </c>
       <c r="I9" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J9" s="3">
         <v>300</v>
       </c>
       <c r="K9" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L9" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M9" s="3">
         <v>200</v>
@@ -835,72 +848,84 @@
         <v>200</v>
       </c>
       <c r="P9" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q9" s="3">
-        <v>0</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="R9" s="3">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F10" s="3">
         <v>1400</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1000</v>
       </c>
       <c r="G10" s="3">
         <v>1000</v>
       </c>
       <c r="H10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J10" s="3">
         <v>1200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>900</v>
-      </c>
-      <c r="K10" s="3">
-        <v>700</v>
-      </c>
-      <c r="L10" s="3">
-        <v>800</v>
       </c>
       <c r="M10" s="3">
         <v>700</v>
       </c>
       <c r="N10" s="3">
+        <v>800</v>
+      </c>
+      <c r="O10" s="3">
         <v>700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>300</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,8 +945,10 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -973,8 +1000,14 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1026,52 +1059,58 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1079,19 +1118,25 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F15" s="3">
         <v>1000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>600</v>
-      </c>
-      <c r="F15" s="3">
-        <v>600</v>
       </c>
       <c r="G15" s="3">
         <v>600</v>
@@ -1103,37 +1148,43 @@
         <v>600</v>
       </c>
       <c r="J15" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="K15" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="L15" s="3">
         <v>400</v>
       </c>
       <c r="M15" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N15" s="3">
         <v>400</v>
       </c>
       <c r="O15" s="3">
+        <v>400</v>
+      </c>
+      <c r="P15" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q15" s="3">
         <v>700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>100</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1150,114 +1201,128 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F17" s="3">
         <v>3100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2300</v>
       </c>
       <c r="H17" s="3">
         <v>2000</v>
       </c>
       <c r="I17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K17" s="3">
         <v>2200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-400</v>
       </c>
       <c r="K18" s="3">
         <v>-800</v>
       </c>
       <c r="L18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="M18" s="3">
-        <v>-200</v>
+        <v>-800</v>
       </c>
       <c r="N18" s="3">
         <v>-300</v>
       </c>
       <c r="O18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-1000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1277,44 +1342,46 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="E20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1324,34 +1391,40 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-300</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-600</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-400</v>
       </c>
       <c r="J21" s="3">
         <v>0</v>
@@ -1360,31 +1433,37 @@
         <v>-400</v>
       </c>
       <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N21" s="3">
         <v>1100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>100</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-500</v>
       </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S21" s="3">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1436,61 +1515,73 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1200</v>
+        <v>-1900</v>
       </c>
       <c r="E23" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="F23" s="3">
         <v>-1200</v>
       </c>
       <c r="G23" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="H23" s="3">
-        <v>-500</v>
+        <v>-1200</v>
       </c>
       <c r="I23" s="3">
         <v>-900</v>
       </c>
       <c r="J23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L23" s="3">
         <v>-400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1542,8 +1633,14 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1595,78 +1692,90 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1200</v>
+        <v>-1900</v>
       </c>
       <c r="E26" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="F26" s="3">
         <v>-1200</v>
       </c>
       <c r="G26" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="H26" s="3">
-        <v>-500</v>
+        <v>-1200</v>
       </c>
       <c r="I26" s="3">
         <v>-900</v>
       </c>
       <c r="J26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L26" s="3">
         <v>-400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1300</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-600</v>
       </c>
       <c r="I27" s="3">
         <v>-1000</v>
@@ -1675,34 +1784,40 @@
         <v>-600</v>
       </c>
       <c r="K27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="M27" s="3">
         <v>-800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1754,8 +1869,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1807,8 +1928,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1860,8 +1987,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1913,44 +2046,50 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E32" s="3">
+        <v>400</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -1960,31 +2099,37 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1300</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-600</v>
       </c>
       <c r="I33" s="3">
         <v>-1000</v>
@@ -1993,34 +2138,40 @@
         <v>-600</v>
       </c>
       <c r="K33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="M33" s="3">
         <v>-800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2072,25 +2223,31 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1300</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-600</v>
       </c>
       <c r="I35" s="3">
         <v>-1000</v>
@@ -2099,92 +2256,104 @@
         <v>-600</v>
       </c>
       <c r="K35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="M35" s="3">
         <v>-800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43921</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43646</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43555</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2204,8 +2373,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2225,50 +2396,52 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F41" s="3">
         <v>4300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>10600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>14200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>900</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2278,8 +2451,14 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2331,8 +2510,14 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2340,16 +2525,16 @@
         <v>300</v>
       </c>
       <c r="E43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G43" s="3">
         <v>100</v>
       </c>
       <c r="H43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3">
         <v>100</v>
@@ -2369,11 +2554,11 @@
       <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
+      <c r="O43" s="3">
+        <v>100</v>
+      </c>
+      <c r="P43" s="3">
+        <v>100</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
@@ -2384,8 +2569,14 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2437,49 +2628,55 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>200</v>
-      </c>
-      <c r="M45" s="3">
-        <v>100</v>
       </c>
       <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
+      <c r="O45" s="3">
+        <v>100</v>
+      </c>
+      <c r="P45" s="3">
+        <v>200</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
@@ -2490,8 +2687,14 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2543,8 +2746,14 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2596,13 +2805,19 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="E48" s="3">
         <v>6200</v>
@@ -2614,32 +2829,32 @@
         <v>6200</v>
       </c>
       <c r="H48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="I48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J48" s="3">
         <v>55800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>56200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>56600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>39000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>34800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>35000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>35300</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,50 +2864,56 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>89300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>97400</v>
+      </c>
+      <c r="F49" s="3">
         <v>99000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>51200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>51700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>52300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>3400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>3600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2500</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2702,8 +2923,14 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2755,8 +2982,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2808,50 +3041,56 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F52" s="3">
         <v>400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>400</v>
       </c>
       <c r="I52" s="3">
         <v>300</v>
       </c>
       <c r="J52" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K52" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L52" s="3">
         <v>200</v>
       </c>
       <c r="M52" s="3">
+        <v>200</v>
+      </c>
+      <c r="N52" s="3">
+        <v>200</v>
+      </c>
+      <c r="O52" s="3">
         <v>600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>500</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2861,8 +3100,14 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2914,50 +3159,56 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>104600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>108700</v>
+      </c>
+      <c r="F54" s="3">
         <v>110800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>62000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>63200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>64200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>63800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>65300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>66600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>53400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>52400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>39000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>39400</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2967,8 +3218,14 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2988,8 +3245,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3009,49 +3268,51 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="G57" s="3">
-        <v>4300</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
-      </c>
-      <c r="L57" s="3">
-        <v>200</v>
-      </c>
-      <c r="M57" s="3">
-        <v>100</v>
       </c>
       <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
+      <c r="O57" s="3">
+        <v>100</v>
+      </c>
+      <c r="P57" s="3">
+        <v>200</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
@@ -3062,8 +3323,14 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3095,17 +3362,17 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>1100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1100</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3115,8 +3382,14 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3124,41 +3397,41 @@
         <v>8100</v>
       </c>
       <c r="E59" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F59" s="3">
+        <v>8100</v>
+      </c>
+      <c r="G59" s="3">
         <v>7500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>7500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>6900</v>
-      </c>
-      <c r="H59" s="3">
-        <v>6800</v>
       </c>
       <c r="I59" s="3">
         <v>6900</v>
       </c>
       <c r="J59" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K59" s="3">
         <v>6900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3168,8 +3441,14 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3221,50 +3500,56 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>62300</v>
+      </c>
+      <c r="F61" s="3">
         <v>62600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>36500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>36600</v>
       </c>
-      <c r="G61" s="3">
-        <v>35200</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>36700</v>
+      </c>
+      <c r="J61" s="3">
         <v>35400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>35500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>35000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>29000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>26800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>27200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>27300</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3274,8 +3559,14 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3327,8 +3618,14 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3380,8 +3677,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3433,8 +3736,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3486,50 +3795,56 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>92700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>93400</v>
+      </c>
+      <c r="F66" s="3">
         <v>93000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>54000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>54000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>53500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>51900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>53700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>53700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>39800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>37700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>37400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>37600</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3539,8 +3854,14 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3560,8 +3881,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3613,8 +3936,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3666,19 +3995,25 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3">
         <v>11600</v>
       </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>11600</v>
       </c>
       <c r="G70" s="3">
         <v>0</v>
@@ -3719,8 +4054,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3772,50 +4113,56 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-12700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-10800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-10000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-8600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-7700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-7000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-6000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-5400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-4600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-3100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-2800</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3825,8 +4172,14 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3878,8 +4231,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3931,8 +4290,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3984,50 +4349,56 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F76" s="3">
         <v>6100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>8100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>9200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>10700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>11900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>11600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>12800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>13700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>14700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1900</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4037,8 +4408,14 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4090,83 +4467,95 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43921</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43646</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43555</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1300</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-600</v>
       </c>
       <c r="I81" s="3">
         <v>-1000</v>
@@ -4175,34 +4564,40 @@
         <v>-600</v>
       </c>
       <c r="K81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="M81" s="3">
         <v>-800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4222,19 +4617,21 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="E83" s="3">
-        <v>600</v>
+        <v>1400</v>
       </c>
       <c r="F83" s="3">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="G83" s="3">
         <v>600</v>
@@ -4246,37 +4643,43 @@
         <v>600</v>
       </c>
       <c r="J83" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="K83" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="L83" s="3">
         <v>400</v>
       </c>
       <c r="M83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N83" s="3">
         <v>400</v>
       </c>
       <c r="O83" s="3">
+        <v>400</v>
+      </c>
+      <c r="P83" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q83" s="3">
         <v>700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4328,8 +4731,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4381,8 +4790,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4434,8 +4849,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4487,8 +4908,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4540,61 +4967,73 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>500</v>
-      </c>
-      <c r="E89" s="3">
-        <v>300</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-900</v>
       </c>
       <c r="G89" s="3">
         <v>300</v>
       </c>
       <c r="H89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I89" s="3">
+        <v>300</v>
+      </c>
+      <c r="J89" s="3">
         <v>400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
         <v>100</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4614,19 +5053,21 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-33300</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -4638,37 +5079,43 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-12800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-4900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-3400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-16700</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4720,8 +5167,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4773,61 +5226,73 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-33100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
       </c>
       <c r="H94" s="3">
         <v>-100</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-12700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-4900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>1200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-16600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>100</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4847,13 +5312,15 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="E96" s="3">
         <v>-300</v>
@@ -4865,22 +5332,22 @@
         <v>-300</v>
       </c>
       <c r="H96" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="I96" s="3">
         <v>-300</v>
       </c>
       <c r="J96" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="K96" s="3">
         <v>-300</v>
       </c>
       <c r="L96" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="M96" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4900,8 +5367,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4953,8 +5426,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5006,8 +5485,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5059,61 +5544,73 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F100" s="3">
         <v>34800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>6900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>1700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>12300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>17600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>700</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5165,57 +5662,69 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F102" s="3">
         <v>2200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-6000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-3600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>13500</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3" t="s">
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GIPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GIPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
   <si>
     <t>GIPR</t>
   </si>
@@ -656,158 +656,165 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43921</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43555</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1800</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1300</v>
       </c>
       <c r="H8" s="3">
         <v>1300</v>
       </c>
       <c r="I8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J8" s="3">
         <v>1400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1000</v>
-      </c>
-      <c r="O8" s="3">
-        <v>900</v>
       </c>
       <c r="P8" s="3">
         <v>900</v>
       </c>
       <c r="Q8" s="3">
+        <v>900</v>
+      </c>
+      <c r="R8" s="3">
         <v>1700</v>
-      </c>
-      <c r="R8" s="3">
-        <v>300</v>
       </c>
       <c r="S8" s="3">
         <v>300</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
+      <c r="T8" s="3">
+        <v>300</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -815,22 +822,22 @@
         <v>700</v>
       </c>
       <c r="E9" s="3">
+        <v>700</v>
+      </c>
+      <c r="F9" s="3">
         <v>600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>300</v>
       </c>
       <c r="H9" s="3">
         <v>300</v>
       </c>
       <c r="I9" s="3">
+        <v>300</v>
+      </c>
+      <c r="J9" s="3">
         <v>400</v>
-      </c>
-      <c r="J9" s="3">
-        <v>300</v>
       </c>
       <c r="K9" s="3">
         <v>300</v>
@@ -839,7 +846,7 @@
         <v>300</v>
       </c>
       <c r="M9" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N9" s="3">
         <v>200</v>
@@ -854,33 +861,36 @@
         <v>200</v>
       </c>
       <c r="R9" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S9" s="3">
         <v>0</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
+      <c r="T9" s="3">
+        <v>0</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E10" s="3">
         <v>1700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1400</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1000</v>
       </c>
       <c r="H10" s="3">
         <v>1000</v>
@@ -889,43 +899,46 @@
         <v>1000</v>
       </c>
       <c r="J10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K10" s="3">
         <v>1200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>800</v>
-      </c>
-      <c r="O10" s="3">
-        <v>700</v>
       </c>
       <c r="P10" s="3">
         <v>700</v>
       </c>
       <c r="Q10" s="3">
+        <v>700</v>
+      </c>
+      <c r="R10" s="3">
         <v>1500</v>
-      </c>
-      <c r="R10" s="3">
-        <v>300</v>
       </c>
       <c r="S10" s="3">
         <v>300</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
+      <c r="T10" s="3">
+        <v>300</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,8 +960,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1006,8 +1020,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,16 +1082,19 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1082,29 +1102,29 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
@@ -1112,8 +1132,8 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1124,8 +1144,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1133,13 +1156,13 @@
         <v>1200</v>
       </c>
       <c r="E15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F15" s="3">
         <v>1400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>600</v>
       </c>
       <c r="H15" s="3">
         <v>600</v>
@@ -1154,13 +1177,13 @@
         <v>600</v>
       </c>
       <c r="L15" s="3">
+        <v>600</v>
+      </c>
+      <c r="M15" s="3">
         <v>400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>300</v>
-      </c>
-      <c r="N15" s="3">
-        <v>400</v>
       </c>
       <c r="O15" s="3">
         <v>400</v>
@@ -1169,22 +1192,25 @@
         <v>400</v>
       </c>
       <c r="Q15" s="3">
+        <v>400</v>
+      </c>
+      <c r="R15" s="3">
         <v>700</v>
-      </c>
-      <c r="R15" s="3">
-        <v>100</v>
       </c>
       <c r="S15" s="3">
         <v>100</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
+      <c r="T15" s="3">
+        <v>100</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1229,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E17" s="3">
         <v>3600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3100</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2000</v>
       </c>
       <c r="H17" s="3">
         <v>2000</v>
       </c>
       <c r="I17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J17" s="3">
         <v>2300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1300</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-700</v>
       </c>
       <c r="H18" s="3">
         <v>-700</v>
       </c>
       <c r="I18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J18" s="3">
         <v>-900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,47 +1377,48 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1397,73 +1431,79 @@
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>200</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-200</v>
       </c>
       <c r="G21" s="3">
         <v>-200</v>
       </c>
       <c r="H21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I21" s="3">
         <v>-600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <v>-400</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
       <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
         <v>-400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>100</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
       <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3">
         <v>-300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-500</v>
       </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
+      <c r="T21" s="3">
+        <v>0</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1521,67 +1561,73 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1639,8 +1685,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,47 +2119,50 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2105,73 +2175,79 @@
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43921</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43555</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,53 +2484,54 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>900</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2457,8 +2544,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2516,8 +2606,11 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2525,19 +2618,19 @@
         <v>300</v>
       </c>
       <c r="E43" s="3">
+        <v>300</v>
+      </c>
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>200</v>
-      </c>
-      <c r="I43" s="3">
-        <v>100</v>
       </c>
       <c r="J43" s="3">
         <v>100</v>
@@ -2560,8 +2653,8 @@
       <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
+      <c r="Q43" s="3">
+        <v>100</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
@@ -2575,8 +2668,11 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2634,53 +2730,56 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>500</v>
+      </c>
+      <c r="E45" s="3">
         <v>600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>500</v>
       </c>
       <c r="H45" s="3">
         <v>500</v>
       </c>
       <c r="I45" s="3">
+        <v>500</v>
+      </c>
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>200</v>
       </c>
       <c r="N45" s="3">
         <v>200</v>
       </c>
       <c r="O45" s="3">
+        <v>200</v>
+      </c>
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,8 +2792,11 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2752,8 +2854,11 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2811,8 +2916,11 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2820,7 +2928,7 @@
         <v>6100</v>
       </c>
       <c r="E48" s="3">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="F48" s="3">
         <v>6200</v>
@@ -2835,29 +2943,29 @@
         <v>6200</v>
       </c>
       <c r="J48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="K48" s="3">
         <v>55800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>56200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>56600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>39000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>35000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>35300</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2870,53 +2978,56 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>88100</v>
+      </c>
+      <c r="E49" s="3">
         <v>89300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>97400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>99000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>51200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>51700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>52300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2500</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2929,8 +3040,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,8 +3164,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3056,28 +3176,28 @@
         <v>6200</v>
       </c>
       <c r="E52" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F52" s="3">
         <v>1100</v>
-      </c>
-      <c r="F52" s="3">
-        <v>400</v>
       </c>
       <c r="G52" s="3">
         <v>400</v>
       </c>
       <c r="H52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I52" s="3">
         <v>300</v>
       </c>
       <c r="J52" s="3">
+        <v>300</v>
+      </c>
+      <c r="K52" s="3">
         <v>400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>300</v>
-      </c>
-      <c r="L52" s="3">
-        <v>200</v>
       </c>
       <c r="M52" s="3">
         <v>200</v>
@@ -3086,14 +3206,14 @@
         <v>200</v>
       </c>
       <c r="O52" s="3">
+        <v>200</v>
+      </c>
+      <c r="P52" s="3">
         <v>600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>500</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3106,8 +3226,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,53 +3288,56 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>104500</v>
+      </c>
+      <c r="E54" s="3">
         <v>104600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>108700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>110800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>62000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>63200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>64200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>63800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>65300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>66600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>53400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>52400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>39000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>39400</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3224,8 +3350,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,53 +3400,54 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2700</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3">
         <v>100</v>
-      </c>
-      <c r="M57" s="3">
-        <v>200</v>
       </c>
       <c r="N57" s="3">
         <v>200</v>
       </c>
       <c r="O57" s="3">
+        <v>200</v>
+      </c>
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3329,8 +3460,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3368,13 +3502,13 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>1100</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
+      <c r="Q58" s="3">
+        <v>1100</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
@@ -3388,53 +3522,56 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E59" s="3">
         <v>8100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8100</v>
-      </c>
-      <c r="G59" s="3">
-        <v>7500</v>
       </c>
       <c r="H59" s="3">
         <v>7500</v>
       </c>
       <c r="I59" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J59" s="3">
         <v>6900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6800</v>
-      </c>
-      <c r="K59" s="3">
-        <v>6900</v>
       </c>
       <c r="L59" s="3">
         <v>6900</v>
       </c>
       <c r="M59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3447,8 +3584,11 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3506,53 +3646,56 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>61800</v>
+      </c>
+      <c r="E61" s="3">
         <v>62000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>62300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>62600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>36500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>36600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>36700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>35400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>35500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>35000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>29000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>26800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>27200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>27300</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3565,8 +3708,11 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3624,8 +3770,11 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,53 +3956,56 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>95400</v>
+      </c>
+      <c r="E66" s="3">
         <v>92700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>93400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>93000</v>
-      </c>
-      <c r="G66" s="3">
-        <v>54000</v>
       </c>
       <c r="H66" s="3">
         <v>54000</v>
       </c>
       <c r="I66" s="3">
+        <v>54000</v>
+      </c>
+      <c r="J66" s="3">
         <v>53500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>51900</v>
-      </c>
-      <c r="K66" s="3">
-        <v>53700</v>
       </c>
       <c r="L66" s="3">
         <v>53700</v>
       </c>
       <c r="M66" s="3">
+        <v>53700</v>
+      </c>
+      <c r="N66" s="3">
         <v>39800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>37700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>37600</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3860,8 +4018,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4010,13 +4178,13 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
-        <v>11600</v>
+        <v>0</v>
       </c>
       <c r="F70" s="3">
         <v>11600</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>11600</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,53 +4290,56 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-17800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-14800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-12700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-10800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-5400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4178,8 +4352,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,53 +4538,56 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E76" s="3">
         <v>11900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4414,8 +4600,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43921</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43555</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,8 +4817,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4628,13 +4827,13 @@
         <v>1200</v>
       </c>
       <c r="E83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F83" s="3">
         <v>1400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>600</v>
       </c>
       <c r="H83" s="3">
         <v>600</v>
@@ -4649,13 +4848,13 @@
         <v>600</v>
       </c>
       <c r="L83" s="3">
+        <v>600</v>
+      </c>
+      <c r="M83" s="3">
         <v>400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>400</v>
       </c>
       <c r="O83" s="3">
         <v>400</v>
@@ -4664,22 +4863,25 @@
         <v>400</v>
       </c>
       <c r="Q83" s="3">
+        <v>400</v>
+      </c>
+      <c r="R83" s="3">
         <v>700</v>
-      </c>
-      <c r="R83" s="3">
-        <v>100</v>
       </c>
       <c r="S83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="T83" s="3">
+        <v>100</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
       </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
       <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>100</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,8 +5275,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5082,29 +5303,29 @@
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-12800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16700</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5114,8 +5335,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,8 +5459,11 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5244,55 +5474,58 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-33100</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-100</v>
       </c>
       <c r="H94" s="3">
         <v>-100</v>
       </c>
       <c r="I94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-16600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>100</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,16 +5547,17 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E96" s="3">
         <v>-500</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-300</v>
       </c>
       <c r="F96" s="3">
         <v>-300</v>
@@ -5338,10 +5572,10 @@
         <v>-300</v>
       </c>
       <c r="J96" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K96" s="3">
         <v>-400</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-300</v>
       </c>
       <c r="L96" s="3">
         <v>-300</v>
@@ -5350,7 +5584,7 @@
         <v>-300</v>
       </c>
       <c r="N96" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,67 +5793,73 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>34800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>12300</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-200</v>
       </c>
       <c r="P100" s="3">
         <v>-200</v>
       </c>
       <c r="Q100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R100" s="3">
         <v>17600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>700</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5668,63 +5917,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>13500</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GIPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GIPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>GIPR</t>
   </si>
@@ -656,165 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43555</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1800</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1300</v>
       </c>
       <c r="I8" s="3">
         <v>1300</v>
       </c>
       <c r="J8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K8" s="3">
         <v>1400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1000</v>
-      </c>
-      <c r="P8" s="3">
-        <v>900</v>
       </c>
       <c r="Q8" s="3">
         <v>900</v>
       </c>
       <c r="R8" s="3">
+        <v>900</v>
+      </c>
+      <c r="S8" s="3">
         <v>1700</v>
-      </c>
-      <c r="S8" s="3">
-        <v>300</v>
       </c>
       <c r="T8" s="3">
         <v>300</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
+      <c r="U8" s="3">
+        <v>300</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -825,22 +832,22 @@
         <v>700</v>
       </c>
       <c r="F9" s="3">
+        <v>700</v>
+      </c>
+      <c r="G9" s="3">
         <v>600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>400</v>
-      </c>
-      <c r="H9" s="3">
-        <v>300</v>
       </c>
       <c r="I9" s="3">
         <v>300</v>
       </c>
       <c r="J9" s="3">
+        <v>300</v>
+      </c>
+      <c r="K9" s="3">
         <v>400</v>
-      </c>
-      <c r="K9" s="3">
-        <v>300</v>
       </c>
       <c r="L9" s="3">
         <v>300</v>
@@ -849,7 +856,7 @@
         <v>300</v>
       </c>
       <c r="N9" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O9" s="3">
         <v>200</v>
@@ -864,36 +871,39 @@
         <v>200</v>
       </c>
       <c r="S9" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T9" s="3">
         <v>0</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
+      <c r="U9" s="3">
+        <v>0</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1600</v>
       </c>
-      <c r="E10" s="3">
-        <v>1700</v>
-      </c>
       <c r="F10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G10" s="3">
         <v>2500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1400</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1000</v>
       </c>
       <c r="I10" s="3">
         <v>1000</v>
@@ -902,43 +912,46 @@
         <v>1000</v>
       </c>
       <c r="K10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L10" s="3">
         <v>1200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>800</v>
-      </c>
-      <c r="P10" s="3">
-        <v>700</v>
       </c>
       <c r="Q10" s="3">
         <v>700</v>
       </c>
       <c r="R10" s="3">
+        <v>700</v>
+      </c>
+      <c r="S10" s="3">
         <v>1500</v>
-      </c>
-      <c r="S10" s="3">
-        <v>300</v>
       </c>
       <c r="T10" s="3">
         <v>300</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
+      <c r="U10" s="3">
+        <v>300</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,8 +974,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1023,8 +1037,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,8 +1102,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1097,37 +1117,37 @@
         <v>3</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+        <v>1100</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
@@ -1135,8 +1155,8 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1147,25 +1167,28 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E15" s="3">
         <v>1200</v>
       </c>
       <c r="F15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G15" s="3">
         <v>1400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>600</v>
       </c>
       <c r="I15" s="3">
         <v>600</v>
@@ -1180,13 +1203,13 @@
         <v>600</v>
       </c>
       <c r="M15" s="3">
+        <v>600</v>
+      </c>
+      <c r="N15" s="3">
         <v>400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>300</v>
-      </c>
-      <c r="O15" s="3">
-        <v>400</v>
       </c>
       <c r="P15" s="3">
         <v>400</v>
@@ -1195,22 +1218,25 @@
         <v>400</v>
       </c>
       <c r="R15" s="3">
+        <v>400</v>
+      </c>
+      <c r="S15" s="3">
         <v>700</v>
-      </c>
-      <c r="S15" s="3">
-        <v>100</v>
       </c>
       <c r="T15" s="3">
         <v>100</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
+      <c r="U15" s="3">
+        <v>100</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1256,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3700</v>
+        <v>2700</v>
       </c>
       <c r="E17" s="3">
-        <v>3600</v>
+        <v>2700</v>
       </c>
       <c r="F17" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
       <c r="G17" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="H17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L17" s="3">
         <v>2000</v>
       </c>
-      <c r="I17" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2300</v>
-      </c>
-      <c r="K17" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>400</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1400</v>
+        <v>-300</v>
       </c>
       <c r="E18" s="3">
-        <v>-1200</v>
+        <v>-400</v>
       </c>
       <c r="F18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G18" s="3">
+        <v>200</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-700</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-900</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,50 +1411,51 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>-400</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>500</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1434,99 +1468,105 @@
       <c r="T20" s="3">
         <v>0</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>300</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K21" s="3">
         <v>-300</v>
       </c>
-      <c r="E21" s="3">
-        <v>-700</v>
-      </c>
-      <c r="F21" s="3">
-        <v>200</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-600</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>100</v>
+      </c>
+      <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
         <v>-300</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="O21" s="3">
-        <v>1100</v>
-      </c>
-      <c r="P21" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-300</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-500</v>
       </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
+      <c r="U21" s="3">
+        <v>0</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1564,93 +1604,99 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1688,8 +1734,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1799,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1994,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2059,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2124,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,50 +2189,53 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>400</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>500</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>100</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2178,76 +2248,82 @@
       <c r="T32" s="3">
         <v>0</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2300</v>
       </c>
-      <c r="E33" s="3">
-        <v>-2900</v>
-      </c>
       <c r="F33" s="3">
-        <v>-2200</v>
+        <v>-2800</v>
       </c>
       <c r="G33" s="3">
-        <v>-1800</v>
+        <v>-1900</v>
       </c>
       <c r="H33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I33" s="3">
         <v>-900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2384,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2300</v>
       </c>
-      <c r="E35" s="3">
-        <v>-2900</v>
-      </c>
       <c r="F35" s="3">
-        <v>-2200</v>
+        <v>-2800</v>
       </c>
       <c r="G35" s="3">
-        <v>-1800</v>
+        <v>-1900</v>
       </c>
       <c r="H35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I35" s="3">
         <v>-900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43555</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2546,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,56 +2571,57 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>900</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2547,22 +2634,25 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -2609,31 +2699,34 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E43" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="F43" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="G43" s="3">
-        <v>300</v>
+        <v>1300</v>
       </c>
       <c r="H43" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="I43" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="J43" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
@@ -2656,8 +2749,8 @@
       <c r="Q43" s="3">
         <v>100</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
+      <c r="R43" s="3">
+        <v>100</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
@@ -2671,31 +2764,34 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2733,56 +2829,59 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="E45" s="3">
-        <v>600</v>
+        <v>6200</v>
       </c>
       <c r="F45" s="3">
+        <v>6300</v>
+      </c>
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>500</v>
       </c>
       <c r="I45" s="3">
         <v>500</v>
       </c>
       <c r="J45" s="3">
+        <v>500</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
-      </c>
-      <c r="N45" s="3">
-        <v>200</v>
       </c>
       <c r="O45" s="3">
         <v>200</v>
       </c>
       <c r="P45" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2795,31 +2894,34 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2857,31 +2959,34 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2919,56 +3024,59 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6100</v>
+        <v>91100</v>
       </c>
       <c r="E48" s="3">
-        <v>6100</v>
+        <v>86800</v>
       </c>
       <c r="F48" s="3">
+        <v>87600</v>
+      </c>
+      <c r="G48" s="3">
+        <v>95600</v>
+      </c>
+      <c r="H48" s="3">
+        <v>96500</v>
+      </c>
+      <c r="I48" s="3">
+        <v>54500</v>
+      </c>
+      <c r="J48" s="3">
+        <v>54900</v>
+      </c>
+      <c r="K48" s="3">
         <v>6200</v>
       </c>
-      <c r="G48" s="3">
-        <v>6200</v>
-      </c>
-      <c r="H48" s="3">
-        <v>6200</v>
-      </c>
-      <c r="I48" s="3">
-        <v>6200</v>
-      </c>
-      <c r="J48" s="3">
-        <v>6200</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>55800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>56200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>56600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>39000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>35000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>35300</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2981,56 +3089,59 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>88100</v>
+        <v>7600</v>
       </c>
       <c r="E49" s="3">
-        <v>89300</v>
+        <v>7400</v>
       </c>
       <c r="F49" s="3">
-        <v>97400</v>
+        <v>7800</v>
       </c>
       <c r="G49" s="3">
-        <v>99000</v>
+        <v>8000</v>
       </c>
       <c r="H49" s="3">
-        <v>51200</v>
+        <v>8700</v>
       </c>
       <c r="I49" s="3">
-        <v>51700</v>
+        <v>2900</v>
       </c>
       <c r="J49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K49" s="3">
         <v>52300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2500</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3043,8 +3154,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3219,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,40 +3284,43 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6200</v>
+        <v>800</v>
       </c>
       <c r="E52" s="3">
-        <v>6200</v>
+        <v>600</v>
       </c>
       <c r="F52" s="3">
-        <v>1100</v>
+        <v>400</v>
       </c>
       <c r="G52" s="3">
         <v>400</v>
       </c>
       <c r="H52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I52" s="3">
         <v>300</v>
       </c>
       <c r="J52" s="3">
+        <v>200</v>
+      </c>
+      <c r="K52" s="3">
         <v>300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>300</v>
-      </c>
-      <c r="M52" s="3">
-        <v>200</v>
       </c>
       <c r="N52" s="3">
         <v>200</v>
@@ -3209,14 +3329,14 @@
         <v>200</v>
       </c>
       <c r="P52" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q52" s="3">
         <v>600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>500</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3229,8 +3349,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,56 +3414,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E54" s="3">
         <v>104500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>104600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>108700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>110800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>62000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>63200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>64200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>63800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>65300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>66600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>53400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>52400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>39000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>39400</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,8 +3479,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3506,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,56 +3531,57 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="E57" s="3">
-        <v>1400</v>
+        <v>300</v>
       </c>
       <c r="F57" s="3">
-        <v>2200</v>
+        <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>2100</v>
+        <v>400</v>
       </c>
       <c r="H57" s="3">
-        <v>2500</v>
+        <v>300</v>
       </c>
       <c r="I57" s="3">
-        <v>2400</v>
+        <v>200</v>
       </c>
       <c r="J57" s="3">
+        <v>100</v>
+      </c>
+      <c r="K57" s="3">
         <v>2800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2700</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3">
         <v>100</v>
-      </c>
-      <c r="N57" s="3">
-        <v>200</v>
       </c>
       <c r="O57" s="3">
         <v>200</v>
       </c>
       <c r="P57" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3463,31 +3594,34 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>11900</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>12200</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>12700</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3505,13 +3639,13 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
         <v>1100</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
+      <c r="R58" s="3">
+        <v>1100</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
@@ -3525,56 +3659,59 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>8200</v>
+        <v>500</v>
       </c>
       <c r="E59" s="3">
-        <v>8100</v>
+        <v>1000</v>
       </c>
       <c r="F59" s="3">
-        <v>7800</v>
+        <v>1500</v>
       </c>
       <c r="G59" s="3">
-        <v>8100</v>
+        <v>1900</v>
       </c>
       <c r="H59" s="3">
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="I59" s="3">
-        <v>7500</v>
+        <v>100</v>
       </c>
       <c r="J59" s="3">
+        <v>100</v>
+      </c>
+      <c r="K59" s="3">
         <v>6900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6800</v>
-      </c>
-      <c r="L59" s="3">
-        <v>6900</v>
       </c>
       <c r="M59" s="3">
         <v>6900</v>
       </c>
       <c r="N59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="O59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3587,31 +3724,34 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>15300</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>15300</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>16400</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3649,56 +3789,59 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>61800</v>
+        <v>58800</v>
       </c>
       <c r="E61" s="3">
-        <v>62000</v>
+        <v>56400</v>
       </c>
       <c r="F61" s="3">
-        <v>62300</v>
+        <v>56500</v>
       </c>
       <c r="G61" s="3">
-        <v>62600</v>
+        <v>56600</v>
       </c>
       <c r="H61" s="3">
-        <v>36500</v>
+        <v>70700</v>
       </c>
       <c r="I61" s="3">
-        <v>36600</v>
+        <v>44900</v>
       </c>
       <c r="J61" s="3">
+        <v>45100</v>
+      </c>
+      <c r="K61" s="3">
         <v>36700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>35400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>35500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>35000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>29000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>26800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>27200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>27300</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3711,31 +3854,34 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3773,8 +3919,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3984,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4049,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,56 +4114,59 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>95400</v>
+        <v>75200</v>
       </c>
       <c r="E66" s="3">
-        <v>92700</v>
+        <v>72500</v>
       </c>
       <c r="F66" s="3">
-        <v>93400</v>
+        <v>72800</v>
       </c>
       <c r="G66" s="3">
-        <v>93000</v>
+        <v>74200</v>
       </c>
       <c r="H66" s="3">
-        <v>54000</v>
+        <v>74200</v>
       </c>
       <c r="I66" s="3">
-        <v>54000</v>
+        <v>47200</v>
       </c>
       <c r="J66" s="3">
+        <v>47200</v>
+      </c>
+      <c r="K66" s="3">
         <v>53500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>51900</v>
-      </c>
-      <c r="L66" s="3">
-        <v>53700</v>
       </c>
       <c r="M66" s="3">
         <v>53700</v>
       </c>
       <c r="N66" s="3">
+        <v>53700</v>
+      </c>
+      <c r="O66" s="3">
         <v>39800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>37400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>37600</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4021,8 +4179,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4206,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4269,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4334,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4181,13 +4349,13 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>11600</v>
+        <v>0</v>
       </c>
       <c r="G70" s="3">
         <v>11600</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>11600</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -4231,8 +4399,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,56 +4464,59 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-20000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-17800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-14800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-12700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-10000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-7000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-5400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-4600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2800</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4355,8 +4529,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4594,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4659,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,56 +4724,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E76" s="3">
         <v>9100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4603,8 +4789,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4854,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43555</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2300</v>
       </c>
-      <c r="E81" s="3">
-        <v>-2900</v>
-      </c>
       <c r="F81" s="3">
-        <v>-2200</v>
+        <v>-2800</v>
       </c>
       <c r="G81" s="3">
-        <v>-1800</v>
+        <v>-1900</v>
       </c>
       <c r="H81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I81" s="3">
         <v>-900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,31 +5016,32 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="E83" s="3">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>1400</v>
+        <v>400</v>
       </c>
       <c r="G83" s="3">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="H83" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="I83" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="J83" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>600</v>
@@ -4851,13 +5050,13 @@
         <v>600</v>
       </c>
       <c r="M83" s="3">
+        <v>600</v>
+      </c>
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>400</v>
       </c>
       <c r="P83" s="3">
         <v>400</v>
@@ -4866,22 +5065,25 @@
         <v>400</v>
       </c>
       <c r="R83" s="3">
+        <v>400</v>
+      </c>
+      <c r="S83" s="3">
         <v>700</v>
-      </c>
-      <c r="S83" s="3">
-        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>100</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5144,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5209,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5274,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5339,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5404,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>600</v>
+      </c>
+      <c r="E89" s="3">
         <v>200</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
       <c r="F89" s="3">
         <v>0</v>
       </c>
       <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
         <v>500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
       <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
         <v>100</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,59 +5496,60 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-33300</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-100</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-12800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16700</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5338,8 +5559,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5624,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5689,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
+        <v>-6000</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-33100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-100</v>
       </c>
       <c r="I94" s="3">
         <v>-100</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-16600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>100</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,37 +5781,38 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-500</v>
+        <v>600</v>
       </c>
       <c r="F96" s="3">
+        <v>500</v>
+      </c>
+      <c r="G96" s="3">
+        <v>300</v>
+      </c>
+      <c r="H96" s="3">
+        <v>300</v>
+      </c>
+      <c r="I96" s="3">
+        <v>300</v>
+      </c>
+      <c r="J96" s="3">
+        <v>300</v>
+      </c>
+      <c r="K96" s="3">
         <v>-300</v>
       </c>
-      <c r="G96" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-300</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-400</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-300</v>
       </c>
       <c r="M96" s="3">
         <v>-300</v>
@@ -5587,7 +5821,7 @@
         <v>-300</v>
       </c>
       <c r="O96" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -5610,8 +5844,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5909,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5974,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,93 +6039,99 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>34800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>12300</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-200</v>
       </c>
       <c r="Q100" s="3">
         <v>-200</v>
       </c>
       <c r="R100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S100" s="3">
         <v>17600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>700</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5920,66 +6169,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E102" s="3">
         <v>900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>13500</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GIPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GIPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>GIPR</t>
   </si>
@@ -656,107 +656,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -764,105 +771,111 @@
         <v>2400</v>
       </c>
       <c r="E8" s="3">
-        <v>2300</v>
+        <v>2700</v>
       </c>
       <c r="F8" s="3">
         <v>2400</v>
       </c>
       <c r="G8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I8" s="3">
         <v>3100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1300</v>
-      </c>
-      <c r="K8" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1500</v>
       </c>
       <c r="M8" s="3">
         <v>1400</v>
       </c>
       <c r="N8" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P8" s="3">
         <v>1200</v>
-      </c>
-      <c r="O8" s="3">
-        <v>900</v>
-      </c>
-      <c r="P8" s="3">
-        <v>1000</v>
       </c>
       <c r="Q8" s="3">
         <v>900</v>
       </c>
       <c r="R8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S8" s="3">
         <v>900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
+        <v>900</v>
+      </c>
+      <c r="U8" s="3">
         <v>1700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>300</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E9" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F9" s="3">
         <v>700</v>
       </c>
       <c r="G9" s="3">
+        <v>700</v>
+      </c>
+      <c r="H9" s="3">
+        <v>700</v>
+      </c>
+      <c r="I9" s="3">
         <v>600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>300</v>
-      </c>
-      <c r="J9" s="3">
-        <v>300</v>
-      </c>
-      <c r="K9" s="3">
-        <v>400</v>
       </c>
       <c r="L9" s="3">
         <v>300</v>
       </c>
       <c r="M9" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N9" s="3">
         <v>300</v>
       </c>
       <c r="O9" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P9" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q9" s="3">
         <v>200</v>
@@ -874,19 +887,25 @@
         <v>200</v>
       </c>
       <c r="T9" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="U9" s="3">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="V9" s="3">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3">
+        <v>0</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -894,64 +913,70 @@
         <v>1700</v>
       </c>
       <c r="E10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G10" s="3">
         <v>1600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>2500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1400</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1000</v>
       </c>
       <c r="K10" s="3">
         <v>1000</v>
       </c>
       <c r="L10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N10" s="3">
         <v>1200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>900</v>
-      </c>
-      <c r="O10" s="3">
-        <v>700</v>
-      </c>
-      <c r="P10" s="3">
-        <v>800</v>
       </c>
       <c r="Q10" s="3">
         <v>700</v>
       </c>
       <c r="R10" s="3">
+        <v>800</v>
+      </c>
+      <c r="S10" s="3">
         <v>700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
+        <v>700</v>
+      </c>
+      <c r="U10" s="3">
         <v>1500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>300</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,8 +1000,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1040,8 +1067,14 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,64 +1138,70 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>1100</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1170,31 +1209,37 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F15" s="3">
         <v>1100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>1200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>1200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>1400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>1000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>600</v>
-      </c>
-      <c r="J15" s="3">
-        <v>600</v>
       </c>
       <c r="K15" s="3">
         <v>600</v>
@@ -1206,37 +1251,43 @@
         <v>600</v>
       </c>
       <c r="N15" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="O15" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="P15" s="3">
         <v>400</v>
       </c>
       <c r="Q15" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="R15" s="3">
         <v>400</v>
       </c>
       <c r="S15" s="3">
+        <v>400</v>
+      </c>
+      <c r="T15" s="3">
+        <v>400</v>
+      </c>
+      <c r="U15" s="3">
         <v>700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>100</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,8 +1308,10 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1266,64 +1319,70 @@
         <v>2700</v>
       </c>
       <c r="E17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F17" s="3">
         <v>2700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H17" s="3">
         <v>2600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>400</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1331,64 +1390,70 @@
         <v>-300</v>
       </c>
       <c r="E18" s="3">
+        <v>100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G18" s="3">
         <v>-400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-500</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-400</v>
       </c>
       <c r="O18" s="3">
         <v>-800</v>
       </c>
       <c r="P18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="Q18" s="3">
-        <v>-200</v>
+        <v>-800</v>
       </c>
       <c r="R18" s="3">
         <v>-300</v>
       </c>
       <c r="S18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U18" s="3">
         <v>-1000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,56 +1477,58 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>300</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
-        <v>400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>1000</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1471,46 +1538,52 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F21" s="3">
         <v>800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1400</v>
       </c>
-      <c r="G21" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J21" s="3">
         <v>500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-300</v>
-      </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-400</v>
       </c>
       <c r="N21" s="3">
         <v>0</v>
@@ -1519,61 +1592,67 @@
         <v>-400</v>
       </c>
       <c r="P21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R21" s="3">
         <v>1100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>100</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3">
         <v>-300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-500</v>
       </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="3">
+        <v>500</v>
+      </c>
+      <c r="F22" s="3">
         <v>1800</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1000</v>
       </c>
       <c r="G22" s="3">
         <v>1000</v>
       </c>
       <c r="H22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>500</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1607,73 +1686,85 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1300</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-800</v>
       </c>
       <c r="J23" s="3">
         <v>-1200</v>
       </c>
       <c r="K23" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="L23" s="3">
-        <v>-500</v>
+        <v>-1200</v>
       </c>
       <c r="M23" s="3">
         <v>-900</v>
       </c>
       <c r="N23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P23" s="3">
         <v>-400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1698,11 +1789,11 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1737,8 +1828,14 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,102 +1899,114 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1300</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-800</v>
       </c>
       <c r="J26" s="3">
         <v>-1200</v>
       </c>
       <c r="K26" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="L26" s="3">
-        <v>-500</v>
+        <v>-1200</v>
       </c>
       <c r="M26" s="3">
         <v>-900</v>
       </c>
       <c r="N26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P26" s="3">
         <v>-400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-2200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1300</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-600</v>
       </c>
       <c r="M27" s="3">
         <v>-1000</v>
@@ -1906,34 +2015,40 @@
         <v>-600</v>
       </c>
       <c r="O27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2112,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2183,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2254,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,56 +2325,62 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2251,43 +2390,49 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1300</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-600</v>
       </c>
       <c r="M33" s="3">
         <v>-1000</v>
@@ -2296,34 +2441,40 @@
         <v>-600</v>
       </c>
       <c r="O33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,37 +2538,43 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1300</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-600</v>
       </c>
       <c r="M35" s="3">
         <v>-1000</v>
@@ -2426,104 +2583,116 @@
         <v>-600</v>
       </c>
       <c r="O35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2716,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,62 +2743,64 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>600</v>
+      </c>
+      <c r="F41" s="3">
         <v>1500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>10600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>14200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>900</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2637,28 +2810,34 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>100</v>
       </c>
       <c r="F42" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G42" s="3">
         <v>100</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -2702,8 +2881,14 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2711,28 +2896,28 @@
         <v>600</v>
       </c>
       <c r="E43" s="3">
+        <v>400</v>
+      </c>
+      <c r="F43" s="3">
+        <v>600</v>
+      </c>
+      <c r="G43" s="3">
         <v>700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>500</v>
-      </c>
-      <c r="K43" s="3">
-        <v>100</v>
-      </c>
-      <c r="L43" s="3">
-        <v>100</v>
       </c>
       <c r="M43" s="3">
         <v>100</v>
@@ -2752,11 +2937,11 @@
       <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
+      <c r="S43" s="3">
+        <v>100</v>
+      </c>
+      <c r="T43" s="3">
+        <v>100</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
@@ -2767,8 +2952,14 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2793,11 +2984,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2832,61 +3023,67 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F45" s="3">
         <v>6000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>6200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>6300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
-      </c>
-      <c r="P45" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>100</v>
       </c>
       <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
+      <c r="S45" s="3">
+        <v>100</v>
+      </c>
+      <c r="T45" s="3">
+        <v>200</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
@@ -2897,38 +3094,44 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F46" s="3">
         <v>8400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>9600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>8800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3800</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2962,8 +3165,14 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2982,18 +3191,18 @@
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>1200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1200</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -3027,62 +3236,68 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>104500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>90700</v>
+      </c>
+      <c r="F48" s="3">
         <v>91100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>86800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>87600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>95600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>96500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>54500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>54900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>6200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>55800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>56200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>56600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>39000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>34800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>35000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>35300</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3092,62 +3307,68 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F49" s="3">
         <v>7600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>7400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>7800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>8000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>8700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>3000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>52300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>3300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>3400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>2400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2500</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3157,8 +3378,14 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3449,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,62 +3520,68 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F52" s="3">
         <v>800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>200</v>
       </c>
       <c r="K52" s="3">
         <v>300</v>
       </c>
       <c r="L52" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="M52" s="3">
         <v>300</v>
       </c>
       <c r="N52" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="O52" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P52" s="3">
         <v>200</v>
       </c>
       <c r="Q52" s="3">
+        <v>200</v>
+      </c>
+      <c r="R52" s="3">
+        <v>200</v>
+      </c>
+      <c r="S52" s="3">
         <v>600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>500</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,8 +3591,14 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,62 +3662,68 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>116700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>106600</v>
+      </c>
+      <c r="F54" s="3">
         <v>108000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>104500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>104600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>108700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>110800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>62000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>63200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>64200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>63800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>65300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>66600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>53400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>52400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>39000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>39400</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3482,8 +3733,14 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3764,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,61 +3791,63 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="E57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
       </c>
       <c r="G57" s="3">
+        <v>300</v>
+      </c>
+      <c r="H57" s="3">
+        <v>100</v>
+      </c>
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2700</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>200</v>
-      </c>
-      <c r="P57" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>100</v>
       </c>
       <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
+      <c r="S57" s="3">
+        <v>100</v>
+      </c>
+      <c r="T57" s="3">
+        <v>200</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
@@ -3597,38 +3858,44 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F58" s="3">
         <v>12500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>11900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>12200</v>
       </c>
-      <c r="G58" s="3">
-        <v>12700</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>500</v>
+      </c>
+      <c r="J58" s="3">
         <v>100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3642,17 +3909,17 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>1100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1100</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3662,62 +3929,68 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
+        <v>200</v>
+      </c>
+      <c r="F59" s="3">
         <v>500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1500</v>
       </c>
-      <c r="G59" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
       <c r="I59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
-      </c>
-      <c r="K59" s="3">
-        <v>6900</v>
-      </c>
-      <c r="L59" s="3">
-        <v>6800</v>
       </c>
       <c r="M59" s="3">
         <v>6900</v>
       </c>
       <c r="N59" s="3">
+        <v>6800</v>
+      </c>
+      <c r="O59" s="3">
         <v>6900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>200</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3727,38 +4000,44 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>15300</v>
+        <v>3400</v>
       </c>
       <c r="E60" s="3">
-        <v>15000</v>
+        <v>3900</v>
       </c>
       <c r="F60" s="3">
         <v>15300</v>
       </c>
       <c r="G60" s="3">
-        <v>16400</v>
+        <v>15000</v>
       </c>
       <c r="H60" s="3">
+        <v>15300</v>
+      </c>
+      <c r="I60" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J60" s="3">
         <v>2100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1500</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3792,62 +4071,68 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>68800</v>
+      </c>
+      <c r="F61" s="3">
         <v>58800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>56400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>56500</v>
       </c>
-      <c r="G61" s="3">
-        <v>56600</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>68700</v>
+      </c>
+      <c r="J61" s="3">
         <v>70700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>44900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>45100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>36700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>35400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>35500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>35000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>29000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>26800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>27200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>27300</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -3857,38 +4142,44 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E62" s="3">
         <v>900</v>
       </c>
       <c r="F62" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="G62" s="3">
         <v>900</v>
       </c>
       <c r="H62" s="3">
+        <v>900</v>
+      </c>
+      <c r="I62" s="3">
         <v>1000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -3922,8 +4213,14 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4284,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4355,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,62 +4426,68 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>81800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>73700</v>
+      </c>
+      <c r="F66" s="3">
         <v>75200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>72500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>72800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>74200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>74200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>47200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>47200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>53500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>51900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>53700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>53700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>39800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>37700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>37400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>37600</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4182,8 +4497,14 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4528,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4595,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4666,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4352,17 +4687,17 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>11600</v>
       </c>
-      <c r="H70" s="3">
+      <c r="J70" s="3">
         <v>11600</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
@@ -4402,8 +4737,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,62 +4808,68 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-23000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-20000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-17800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-14800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-12700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-10800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-10000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-8600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-7700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-7000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-6000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-5400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-3100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-2800</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4532,8 +4879,14 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4950,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +5021,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,62 +5092,68 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F76" s="3">
         <v>6200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>9100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>9200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>10700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>11900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>11600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>12800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>13700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>14700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4792,8 +5163,14 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,107 +5234,119 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1300</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-600</v>
       </c>
       <c r="M81" s="3">
         <v>-1000</v>
@@ -4966,34 +5355,40 @@
         <v>-600</v>
       </c>
       <c r="O81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,22 +5412,24 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>800</v>
+      </c>
+      <c r="F83" s="3">
         <v>500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>200</v>
-      </c>
-      <c r="F83" s="3">
-        <v>400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>400</v>
       </c>
       <c r="H83" s="3">
         <v>400</v>
@@ -5041,49 +5438,55 @@
         <v>400</v>
       </c>
       <c r="J83" s="3">
+        <v>400</v>
+      </c>
+      <c r="K83" s="3">
+        <v>400</v>
+      </c>
+      <c r="L83" s="3">
         <v>300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>600</v>
-      </c>
-      <c r="L83" s="3">
-        <v>600</v>
       </c>
       <c r="M83" s="3">
         <v>600</v>
       </c>
       <c r="N83" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="O83" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="P83" s="3">
         <v>400</v>
       </c>
       <c r="Q83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="R83" s="3">
         <v>400</v>
       </c>
       <c r="S83" s="3">
+        <v>400</v>
+      </c>
+      <c r="T83" s="3">
+        <v>400</v>
+      </c>
+      <c r="U83" s="3">
         <v>700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>100</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5550,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5621,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5692,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5763,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,73 +5834,85 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E89" s="3">
         <v>200</v>
       </c>
       <c r="F89" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G89" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>500</v>
-      </c>
-      <c r="I89" s="3">
-        <v>300</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-900</v>
       </c>
       <c r="K89" s="3">
         <v>300</v>
       </c>
       <c r="L89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M89" s="3">
+        <v>300</v>
+      </c>
+      <c r="N89" s="3">
         <v>400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>100</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>-300</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,8 +5936,10 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5523,47 +5964,53 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-12800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-4900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-16700</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +6074,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,73 +6145,85 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
+        <v>200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-6000</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-33100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
       </c>
       <c r="L94" s="3">
         <v>-100</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-12700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-4900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>1200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-16600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>100</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,25 +6247,27 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>500</v>
-      </c>
-      <c r="G96" s="3">
-        <v>300</v>
-      </c>
-      <c r="H96" s="3">
-        <v>300</v>
       </c>
       <c r="I96" s="3">
         <v>300</v>
@@ -5809,25 +6276,25 @@
         <v>300</v>
       </c>
       <c r="K96" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="L96" s="3">
-        <v>-400</v>
+        <v>300</v>
       </c>
       <c r="M96" s="3">
         <v>-300</v>
       </c>
       <c r="N96" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="O96" s="3">
         <v>-300</v>
       </c>
       <c r="P96" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="Q96" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -5847,8 +6314,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6385,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6456,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,73 +6527,85 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F100" s="3">
         <v>4400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>34800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>6900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>1700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>12300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>17600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>700</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6133,11 +6630,11 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6172,69 +6669,81 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>2200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-6000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-3600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>13500</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W102" s="3" t="s">
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GIPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GIPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>GIPR</t>
   </si>
@@ -656,114 +656,118 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -771,81 +775,84 @@
         <v>2400</v>
       </c>
       <c r="E8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F8" s="3">
         <v>2700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1800</v>
-      </c>
-      <c r="K8" s="3">
-        <v>1300</v>
       </c>
       <c r="L8" s="3">
         <v>1300</v>
       </c>
       <c r="M8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N8" s="3">
         <v>1400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1000</v>
-      </c>
-      <c r="S8" s="3">
-        <v>900</v>
       </c>
       <c r="T8" s="3">
         <v>900</v>
       </c>
       <c r="U8" s="3">
+        <v>900</v>
+      </c>
+      <c r="V8" s="3">
         <v>1700</v>
-      </c>
-      <c r="V8" s="3">
-        <v>300</v>
       </c>
       <c r="W8" s="3">
         <v>300</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
+      <c r="X8" s="3">
+        <v>300</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E9" s="3">
         <v>600</v>
       </c>
       <c r="F9" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G9" s="3">
         <v>700</v>
@@ -854,22 +861,22 @@
         <v>700</v>
       </c>
       <c r="I9" s="3">
+        <v>700</v>
+      </c>
+      <c r="J9" s="3">
         <v>600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>400</v>
-      </c>
-      <c r="K9" s="3">
-        <v>300</v>
       </c>
       <c r="L9" s="3">
         <v>300</v>
       </c>
       <c r="M9" s="3">
+        <v>300</v>
+      </c>
+      <c r="N9" s="3">
         <v>400</v>
-      </c>
-      <c r="N9" s="3">
-        <v>300</v>
       </c>
       <c r="O9" s="3">
         <v>300</v>
@@ -878,7 +885,7 @@
         <v>300</v>
       </c>
       <c r="Q9" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R9" s="3">
         <v>200</v>
@@ -893,19 +900,22 @@
         <v>200</v>
       </c>
       <c r="V9" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W9" s="3">
         <v>0</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
+      <c r="X9" s="3">
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -913,25 +923,25 @@
         <v>1700</v>
       </c>
       <c r="E10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F10" s="3">
         <v>2100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1400</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1000</v>
       </c>
       <c r="L10" s="3">
         <v>1000</v>
@@ -940,43 +950,46 @@
         <v>1000</v>
       </c>
       <c r="N10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O10" s="3">
         <v>1200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>800</v>
-      </c>
-      <c r="S10" s="3">
-        <v>700</v>
       </c>
       <c r="T10" s="3">
         <v>700</v>
       </c>
       <c r="U10" s="3">
+        <v>700</v>
+      </c>
+      <c r="V10" s="3">
         <v>1500</v>
-      </c>
-      <c r="V10" s="3">
-        <v>300</v>
       </c>
       <c r="W10" s="3">
         <v>300</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
+      <c r="X10" s="3">
+        <v>300</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1015,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1087,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,29 +1161,32 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>1100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1176,26 +1196,26 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
@@ -1203,8 +1223,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1215,8 +1235,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1227,22 +1250,22 @@
         <v>1300</v>
       </c>
       <c r="F15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G15" s="3">
         <v>1100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1200</v>
       </c>
       <c r="H15" s="3">
         <v>1200</v>
       </c>
       <c r="I15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J15" s="3">
         <v>1400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>600</v>
       </c>
       <c r="L15" s="3">
         <v>600</v>
@@ -1257,13 +1280,13 @@
         <v>600</v>
       </c>
       <c r="P15" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q15" s="3">
         <v>400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>300</v>
-      </c>
-      <c r="R15" s="3">
-        <v>400</v>
       </c>
       <c r="S15" s="3">
         <v>400</v>
@@ -1272,22 +1295,25 @@
         <v>400</v>
       </c>
       <c r="U15" s="3">
+        <v>400</v>
+      </c>
+      <c r="V15" s="3">
         <v>700</v>
-      </c>
-      <c r="V15" s="3">
-        <v>100</v>
       </c>
       <c r="W15" s="3">
         <v>100</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
+      <c r="X15" s="3">
+        <v>100</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,8 +1336,9 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1319,70 +1346,73 @@
         <v>2700</v>
       </c>
       <c r="E17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F17" s="3">
         <v>2600</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2700</v>
       </c>
       <c r="G17" s="3">
         <v>2700</v>
       </c>
       <c r="H17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I17" s="3">
         <v>2600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>400</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1390,70 +1420,73 @@
         <v>-300</v>
       </c>
       <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
         <v>100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-400</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-200</v>
       </c>
       <c r="L18" s="3">
         <v>-200</v>
       </c>
       <c r="M18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N18" s="3">
         <v>-900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-100</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,59 +1512,60 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>1000</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1544,117 +1578,123 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
+      <c r="X20" s="3">
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>900</v>
+      </c>
+      <c r="E21" s="3">
         <v>700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-300</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
       <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
         <v>-400</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
       <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3">
         <v>-400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>100</v>
       </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
       <c r="U21" s="3">
+        <v>0</v>
+      </c>
+      <c r="V21" s="3">
         <v>-300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-500</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
+      <c r="X21" s="3">
+        <v>0</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E22" s="3">
         <v>1200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1800</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1000</v>
       </c>
       <c r="H22" s="3">
         <v>1000</v>
       </c>
       <c r="I22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>800</v>
-      </c>
-      <c r="K22" s="3">
-        <v>500</v>
       </c>
       <c r="L22" s="3">
         <v>500</v>
       </c>
       <c r="M22" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1692,79 +1732,85 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-100</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1795,8 +1841,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1834,8 +1880,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-100</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,59 +2398,62 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-1000</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2396,85 +2466,91 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
+      <c r="X32" s="3">
+        <v>0</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,65 +2831,66 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E41" s="3">
         <v>600</v>
       </c>
       <c r="F41" s="3">
+        <v>600</v>
+      </c>
+      <c r="G41" s="3">
         <v>1500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>14200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>900</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2816,8 +2903,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2828,10 +2918,10 @@
         <v>100</v>
       </c>
       <c r="F42" s="3">
+        <v>100</v>
+      </c>
+      <c r="G42" s="3">
         <v>200</v>
-      </c>
-      <c r="G42" s="3">
-        <v>100</v>
       </c>
       <c r="H42" s="3">
         <v>100</v>
@@ -2840,7 +2930,7 @@
         <v>100</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2887,40 +2977,43 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
         <v>600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>600</v>
-      </c>
-      <c r="G43" s="3">
-        <v>700</v>
       </c>
       <c r="H43" s="3">
         <v>700</v>
       </c>
       <c r="I43" s="3">
+        <v>700</v>
+      </c>
+      <c r="J43" s="3">
         <v>1300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>500</v>
-      </c>
-      <c r="M43" s="3">
-        <v>100</v>
       </c>
       <c r="N43" s="3">
         <v>100</v>
@@ -2943,8 +3036,8 @@
       <c r="T43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
+      <c r="U43" s="3">
+        <v>100</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
@@ -2958,8 +3051,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2990,8 +3086,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3029,65 +3125,68 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E45" s="3">
         <v>9900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>300</v>
-      </c>
-      <c r="K45" s="3">
-        <v>500</v>
       </c>
       <c r="L45" s="3">
         <v>500</v>
       </c>
       <c r="M45" s="3">
+        <v>500</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>200</v>
       </c>
       <c r="R45" s="3">
         <v>200</v>
       </c>
       <c r="S45" s="3">
+        <v>200</v>
+      </c>
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3100,41 +3199,44 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>11100</v>
+        <v>3800</v>
       </c>
       <c r="E46" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F46" s="3">
         <v>8000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3800</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -3171,8 +3273,11 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3197,14 +3302,14 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>1200</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>1200</v>
       </c>
       <c r="M47" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3242,65 +3347,68 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>104500</v>
+        <v>89400</v>
       </c>
       <c r="E48" s="3">
+        <v>96600</v>
+      </c>
+      <c r="F48" s="3">
         <v>90700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>91100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>86800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>87600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>95600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>96500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>54500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>54900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>55800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>56200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>56600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>39000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>34800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>35000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>35300</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3313,65 +3421,68 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>11100</v>
       </c>
       <c r="E49" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F49" s="3">
         <v>6700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>52300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2500</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3384,8 +3495,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,49 +3643,52 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="E52" s="3">
+        <v>900</v>
+      </c>
+      <c r="F52" s="3">
         <v>1100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>400</v>
       </c>
       <c r="I52" s="3">
         <v>400</v>
       </c>
       <c r="J52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K52" s="3">
         <v>300</v>
       </c>
       <c r="L52" s="3">
+        <v>300</v>
+      </c>
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>300</v>
-      </c>
-      <c r="P52" s="3">
-        <v>200</v>
       </c>
       <c r="Q52" s="3">
         <v>200</v>
@@ -3577,14 +3697,14 @@
         <v>200</v>
       </c>
       <c r="S52" s="3">
+        <v>200</v>
+      </c>
+      <c r="T52" s="3">
         <v>600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>500</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3597,8 +3717,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,65 +3791,68 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E54" s="3">
         <v>116700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>106600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>108000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>104500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>104600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>108700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>110800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>62000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>63200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>64200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>63800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>65300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>66600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>53400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>52400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>39000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>39400</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3739,8 +3865,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,65 +3923,66 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
         <v>100</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>200</v>
       </c>
       <c r="R57" s="3">
         <v>200</v>
       </c>
       <c r="S57" s="3">
+        <v>200</v>
+      </c>
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>200</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,40 +3995,43 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>1700</v>
       </c>
       <c r="F58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G58" s="3">
         <v>12500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>100</v>
-      </c>
-      <c r="K58" s="3">
-        <v>200</v>
       </c>
       <c r="L58" s="3">
         <v>200</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3915,13 +4049,13 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
         <v>1100</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
+      <c r="U58" s="3">
+        <v>1100</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
@@ -3935,65 +4069,68 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>500</v>
       </c>
       <c r="E59" s="3">
+        <v>100</v>
+      </c>
+      <c r="F59" s="3">
         <v>200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1800</v>
       </c>
-      <c r="J59" s="3">
-        <v>0</v>
-      </c>
       <c r="K59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L59" s="3">
         <v>100</v>
       </c>
       <c r="M59" s="3">
+        <v>100</v>
+      </c>
+      <c r="N59" s="3">
         <v>6900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6800</v>
-      </c>
-      <c r="O59" s="3">
-        <v>6900</v>
       </c>
       <c r="P59" s="3">
         <v>6900</v>
       </c>
       <c r="Q59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>200</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4006,41 +4143,44 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="E60" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F60" s="3">
         <v>3900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1500</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -4077,65 +4217,68 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>76600</v>
+        <v>68900</v>
       </c>
       <c r="E61" s="3">
+        <v>75300</v>
+      </c>
+      <c r="F61" s="3">
         <v>68800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>58800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>56400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>56500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>68700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>70700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>44900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>45100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>36700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>35400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>35500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>35000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>29000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>26800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>27200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>27300</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4148,8 +4291,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4157,31 +4303,31 @@
         <v>1500</v>
       </c>
       <c r="E62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F62" s="3">
         <v>900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>900</v>
       </c>
       <c r="H62" s="3">
         <v>900</v>
       </c>
       <c r="I62" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="J62" s="3">
         <v>1000</v>
       </c>
       <c r="K62" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L62" s="3">
         <v>500</v>
       </c>
       <c r="M62" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,65 +4587,68 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E66" s="3">
         <v>81800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>73700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>75200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>72500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>72800</v>
-      </c>
-      <c r="I66" s="3">
-        <v>74200</v>
       </c>
       <c r="J66" s="3">
         <v>74200</v>
       </c>
       <c r="K66" s="3">
-        <v>47200</v>
+        <v>74200</v>
       </c>
       <c r="L66" s="3">
         <v>47200</v>
       </c>
       <c r="M66" s="3">
+        <v>47200</v>
+      </c>
+      <c r="N66" s="3">
         <v>53500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>51900</v>
-      </c>
-      <c r="O66" s="3">
-        <v>53700</v>
       </c>
       <c r="P66" s="3">
         <v>53700</v>
       </c>
       <c r="Q66" s="3">
+        <v>53700</v>
+      </c>
+      <c r="R66" s="3">
         <v>39800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>37700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>37400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>37600</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,8 +4661,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4693,13 +4861,13 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>11600</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3">
         <v>11600</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>11600</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,65 +4985,68 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-26000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-23300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-23000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-20000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-17800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-14800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-12700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-10800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-10000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-8600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-4600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2800</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4885,8 +5059,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,65 +5281,68 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E76" s="3">
         <v>3100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5169,8 +5355,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,25 +5612,26 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>800</v>
+      </c>
+      <c r="E83" s="3">
         <v>700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>200</v>
-      </c>
-      <c r="H83" s="3">
-        <v>400</v>
       </c>
       <c r="I83" s="3">
         <v>400</v>
@@ -5444,10 +5643,10 @@
         <v>400</v>
       </c>
       <c r="L83" s="3">
+        <v>400</v>
+      </c>
+      <c r="M83" s="3">
         <v>300</v>
-      </c>
-      <c r="M83" s="3">
-        <v>600</v>
       </c>
       <c r="N83" s="3">
         <v>600</v>
@@ -5456,13 +5655,13 @@
         <v>600</v>
       </c>
       <c r="P83" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q83" s="3">
         <v>400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>300</v>
-      </c>
-      <c r="R83" s="3">
-        <v>400</v>
       </c>
       <c r="S83" s="3">
         <v>400</v>
@@ -5471,22 +5670,25 @@
         <v>400</v>
       </c>
       <c r="U83" s="3">
+        <v>400</v>
+      </c>
+      <c r="V83" s="3">
         <v>700</v>
-      </c>
-      <c r="V83" s="3">
-        <v>100</v>
       </c>
       <c r="W83" s="3">
         <v>100</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
+      <c r="X83" s="3">
+        <v>100</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6054,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E89" s="3">
         <v>700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>200</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
       <c r="I89" s="3">
         <v>0</v>
       </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>100</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>-200</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>-300</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,8 +6158,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5970,36 +6191,36 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>-100</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-16700</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6009,8 +6230,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6378,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="D94" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3">
         <v>200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6000</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-33100</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-100</v>
       </c>
       <c r="L94" s="3">
         <v>-100</v>
       </c>
       <c r="M94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-16600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>100</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,28 +6482,29 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>500</v>
-      </c>
-      <c r="I96" s="3">
-        <v>300</v>
       </c>
       <c r="J96" s="3">
         <v>300</v>
@@ -6282,13 +6516,13 @@
         <v>300</v>
       </c>
       <c r="M96" s="3">
+        <v>300</v>
+      </c>
+      <c r="N96" s="3">
         <v>-300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-400</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-300</v>
       </c>
       <c r="P96" s="3">
         <v>-300</v>
@@ -6297,7 +6531,7 @@
         <v>-300</v>
       </c>
       <c r="R96" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,79 +6776,85 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>34800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>6900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>12300</v>
-      </c>
-      <c r="S100" s="3">
-        <v>-200</v>
       </c>
       <c r="T100" s="3">
         <v>-200</v>
       </c>
       <c r="U100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V100" s="3">
         <v>17600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>700</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
+      <c r="X100" s="3">
+        <v>0</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6636,8 +6885,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6675,75 +6924,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>13500</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>-400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GIPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GIPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
   <si>
     <t>GIPR</t>
   </si>
@@ -656,252 +656,265 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E8" s="3">
         <v>2500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G8" s="3">
         <v>2400</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G8" s="3">
-        <v>2700</v>
       </c>
       <c r="H8" s="3">
         <v>2400</v>
       </c>
       <c r="I8" s="3">
-        <v>2300</v>
+        <v>2700</v>
       </c>
       <c r="J8" s="3">
         <v>2400</v>
       </c>
       <c r="K8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="M8" s="3">
         <v>3100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1300</v>
-      </c>
-      <c r="O8" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P8" s="3">
-        <v>1500</v>
       </c>
       <c r="Q8" s="3">
         <v>1400</v>
       </c>
       <c r="R8" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T8" s="3">
         <v>1200</v>
-      </c>
-      <c r="S8" s="3">
-        <v>900</v>
-      </c>
-      <c r="T8" s="3">
-        <v>1000</v>
       </c>
       <c r="U8" s="3">
         <v>900</v>
       </c>
       <c r="V8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W8" s="3">
         <v>900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
+        <v>900</v>
+      </c>
+      <c r="Y8" s="3">
         <v>1700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>300</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>500</v>
+      </c>
+      <c r="E9" s="3">
         <v>600</v>
-      </c>
-      <c r="E9" s="3">
-        <v>700</v>
       </c>
       <c r="F9" s="3">
         <v>600</v>
       </c>
       <c r="G9" s="3">
+        <v>700</v>
+      </c>
+      <c r="H9" s="3">
         <v>600</v>
       </c>
-      <c r="H9" s="3">
-        <v>700</v>
-      </c>
       <c r="I9" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="J9" s="3">
         <v>700</v>
       </c>
       <c r="K9" s="3">
+        <v>700</v>
+      </c>
+      <c r="L9" s="3">
+        <v>700</v>
+      </c>
+      <c r="M9" s="3">
         <v>600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>300</v>
-      </c>
-      <c r="N9" s="3">
-        <v>300</v>
-      </c>
-      <c r="O9" s="3">
-        <v>400</v>
       </c>
       <c r="P9" s="3">
         <v>300</v>
       </c>
       <c r="Q9" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R9" s="3">
         <v>300</v>
       </c>
       <c r="S9" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T9" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U9" s="3">
         <v>200</v>
@@ -913,96 +926,108 @@
         <v>200</v>
       </c>
       <c r="X9" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Y9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F10" s="3">
         <v>1800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1700</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2100</v>
       </c>
       <c r="H10" s="3">
         <v>1700</v>
       </c>
       <c r="I10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K10" s="3">
         <v>1600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>2500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1400</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1000</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1000</v>
       </c>
       <c r="O10" s="3">
         <v>1000</v>
       </c>
       <c r="P10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R10" s="3">
         <v>1200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>900</v>
-      </c>
-      <c r="S10" s="3">
-        <v>700</v>
-      </c>
-      <c r="T10" s="3">
-        <v>800</v>
       </c>
       <c r="U10" s="3">
         <v>700</v>
       </c>
       <c r="V10" s="3">
+        <v>800</v>
+      </c>
+      <c r="W10" s="3">
         <v>700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y10" s="3">
         <v>1500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>300</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,8 +1055,10 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1107,8 +1134,14 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,76 +1217,82 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>200</v>
       </c>
       <c r="E14" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>-1000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>1100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1261,16 +1300,22 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="E15" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F15" s="3">
         <v>1300</v>
@@ -1279,25 +1324,25 @@
         <v>1300</v>
       </c>
       <c r="H15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J15" s="3">
         <v>1100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>1200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>1200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>1400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>1000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>600</v>
-      </c>
-      <c r="N15" s="3">
-        <v>600</v>
       </c>
       <c r="O15" s="3">
         <v>600</v>
@@ -1309,37 +1354,43 @@
         <v>600</v>
       </c>
       <c r="R15" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="S15" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="T15" s="3">
         <v>400</v>
       </c>
       <c r="U15" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="V15" s="3">
         <v>400</v>
       </c>
       <c r="W15" s="3">
+        <v>400</v>
+      </c>
+      <c r="X15" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y15" s="3">
         <v>700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>100</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1415,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F17" s="3">
         <v>3000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2700</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2600</v>
       </c>
       <c r="H17" s="3">
         <v>2700</v>
       </c>
       <c r="I17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J17" s="3">
         <v>2700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L17" s="3">
         <v>2600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>400</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-300</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G18" s="3">
-        <v>100</v>
       </c>
       <c r="H18" s="3">
         <v>-300</v>
       </c>
       <c r="I18" s="3">
+        <v>100</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-500</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-400</v>
       </c>
       <c r="S18" s="3">
         <v>-800</v>
       </c>
       <c r="T18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="U18" s="3">
-        <v>-200</v>
+        <v>-800</v>
       </c>
       <c r="V18" s="3">
         <v>-300</v>
       </c>
       <c r="W18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-1000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-100</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,68 +1612,70 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E20" s="3">
+        <v>400</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
         <v>-400</v>
       </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>1000</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1618,58 +1685,64 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E21" s="3">
         <v>700</v>
-      </c>
-      <c r="E21" s="3">
-        <v>900</v>
       </c>
       <c r="F21" s="3">
         <v>700</v>
       </c>
       <c r="G21" s="3">
-        <v>1300</v>
+        <v>900</v>
       </c>
       <c r="H21" s="3">
+        <v>700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J21" s="3">
         <v>800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-300</v>
-      </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-400</v>
       </c>
       <c r="R21" s="3">
         <v>0</v>
@@ -1678,73 +1751,79 @@
         <v>-400</v>
       </c>
       <c r="T21" s="3">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V21" s="3">
         <v>1100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>100</v>
       </c>
-      <c r="V21" s="3">
-        <v>0</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-500</v>
       </c>
-      <c r="Y21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E22" s="3">
-        <v>2100</v>
+        <v>600</v>
       </c>
       <c r="F22" s="3">
         <v>1200</v>
       </c>
       <c r="G22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I22" s="3">
+        <v>600</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N22" s="3">
+        <v>800</v>
+      </c>
+      <c r="O22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L22" s="3">
-        <v>800</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="P22" s="3">
         <v>500</v>
       </c>
-      <c r="N22" s="3">
-        <v>500</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -1778,85 +1857,97 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1300</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-800</v>
       </c>
       <c r="N23" s="3">
         <v>-1200</v>
       </c>
       <c r="O23" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="P23" s="3">
-        <v>-500</v>
+        <v>-1200</v>
       </c>
       <c r="Q23" s="3">
         <v>-900</v>
       </c>
       <c r="R23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="T23" s="3">
         <v>-400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-100</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1893,11 +1984,11 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1932,8 +2023,14 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,126 +2106,138 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1300</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-800</v>
       </c>
       <c r="N26" s="3">
         <v>-1200</v>
       </c>
       <c r="O26" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="P26" s="3">
-        <v>-500</v>
+        <v>-1200</v>
       </c>
       <c r="Q26" s="3">
         <v>-900</v>
       </c>
       <c r="R26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="T26" s="3">
         <v>-400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-4400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-600</v>
       </c>
       <c r="Q27" s="3">
         <v>-1000</v>
@@ -2137,34 +2246,40 @@
         <v>-600</v>
       </c>
       <c r="S27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="T27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U27" s="3">
         <v>-800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-200</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2355,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2438,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2521,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,68 +2604,74 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
         <v>400</v>
       </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1000</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -2542,55 +2681,61 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-4400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-600</v>
       </c>
       <c r="Q33" s="3">
         <v>-1000</v>
@@ -2599,34 +2744,40 @@
         <v>-600</v>
       </c>
       <c r="S33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="T33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U33" s="3">
         <v>-800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-200</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,49 +2853,55 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-4400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-600</v>
       </c>
       <c r="Q35" s="3">
         <v>-1000</v>
@@ -2753,116 +2910,128 @@
         <v>-600</v>
       </c>
       <c r="S35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="T35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U35" s="3">
         <v>-800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-200</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +3059,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,74 +3090,76 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F41" s="3">
         <v>200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>3600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>4600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>10600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>14200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>900</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2996,8 +3169,14 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3014,22 +3193,22 @@
         <v>100</v>
       </c>
       <c r="H42" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I42" s="3">
         <v>100</v>
       </c>
       <c r="J42" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K42" s="3">
         <v>100</v>
       </c>
       <c r="L42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -3073,8 +3252,14 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3085,7 +3270,7 @@
         <v>400</v>
       </c>
       <c r="F43" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="G43" s="3">
         <v>400</v>
@@ -3094,28 +3279,28 @@
         <v>600</v>
       </c>
       <c r="I43" s="3">
+        <v>400</v>
+      </c>
+      <c r="J43" s="3">
+        <v>600</v>
+      </c>
+      <c r="K43" s="3">
         <v>700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>500</v>
-      </c>
-      <c r="O43" s="3">
-        <v>100</v>
-      </c>
-      <c r="P43" s="3">
-        <v>100</v>
       </c>
       <c r="Q43" s="3">
         <v>100</v>
@@ -3135,11 +3320,11 @@
       <c r="V43" s="3">
         <v>100</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
+      <c r="W43" s="3">
+        <v>100</v>
+      </c>
+      <c r="X43" s="3">
+        <v>100</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
@@ -3150,8 +3335,14 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3188,11 +3379,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3227,73 +3418,79 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>200</v>
+      </c>
+      <c r="F45" s="3">
         <v>11100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>9900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>6900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>6000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>6200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>6300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
-      </c>
-      <c r="T45" s="3">
-        <v>200</v>
-      </c>
-      <c r="U45" s="3">
-        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
+      <c r="W45" s="3">
+        <v>100</v>
+      </c>
+      <c r="X45" s="3">
+        <v>200</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
@@ -3304,50 +3501,56 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F46" s="3">
         <v>11800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>11200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>8000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>8400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>9600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>8800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>5300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3800</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3381,8 +3584,14 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3413,18 +3622,18 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3">
         <v>1200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1200</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -3458,74 +3667,80 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>80700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>84500</v>
+      </c>
+      <c r="F48" s="3">
         <v>85400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>93000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>96600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>90700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>91100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>86800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>87600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>95600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>96500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>54500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>54900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>6200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>55800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>56200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>56600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>39000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>34800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>35000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>35300</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3535,74 +3750,80 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F49" s="3">
         <v>5600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>7500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>7900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>6700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>7600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>7400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>7800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>8000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>8700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>52300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>3300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>3400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>3600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>2300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>2100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>2400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>2500</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3612,8 +3833,14 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3916,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,74 +3999,80 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>700</v>
+      </c>
+      <c r="F52" s="3">
         <v>600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>300</v>
-      </c>
-      <c r="M52" s="3">
-        <v>300</v>
-      </c>
-      <c r="N52" s="3">
-        <v>200</v>
       </c>
       <c r="O52" s="3">
         <v>300</v>
       </c>
       <c r="P52" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="Q52" s="3">
         <v>300</v>
       </c>
       <c r="R52" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="S52" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T52" s="3">
         <v>200</v>
       </c>
       <c r="U52" s="3">
+        <v>200</v>
+      </c>
+      <c r="V52" s="3">
+        <v>200</v>
+      </c>
+      <c r="W52" s="3">
         <v>600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>500</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3843,8 +4082,14 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,74 +4165,80 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>88300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>97300</v>
+      </c>
+      <c r="F54" s="3">
         <v>103400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>105000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>116700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>106600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>108000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>104500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>104600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>108700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>110800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>62000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>63200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>64200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>63800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>65300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>66600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>53400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>52400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>39000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>39400</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3997,8 +4248,14 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4283,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,73 +4314,75 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>600</v>
+        <v>1600</v>
       </c>
       <c r="E57" s="3">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="F57" s="3">
         <v>600</v>
       </c>
       <c r="G57" s="3">
+        <v>400</v>
+      </c>
+      <c r="H57" s="3">
+        <v>600</v>
+      </c>
+      <c r="I57" s="3">
         <v>200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>300</v>
       </c>
       <c r="J57" s="3">
         <v>100</v>
       </c>
       <c r="K57" s="3">
+        <v>300</v>
+      </c>
+      <c r="L57" s="3">
+        <v>100</v>
+      </c>
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2700</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>200</v>
-      </c>
-      <c r="T57" s="3">
-        <v>200</v>
-      </c>
-      <c r="U57" s="3">
-        <v>100</v>
       </c>
       <c r="V57" s="3">
         <v>200</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
+      <c r="W57" s="3">
+        <v>100</v>
+      </c>
+      <c r="X57" s="3">
+        <v>200</v>
       </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
@@ -4132,50 +4393,56 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F58" s="3">
         <v>3000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1700</v>
       </c>
-      <c r="G58" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>200</v>
+      </c>
+      <c r="J58" s="3">
         <v>12500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>11900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>12200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>200</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4189,17 +4456,17 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>1100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1100</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4209,74 +4476,80 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
+        <v>200</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
-        <v>200</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1800</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
         <v>100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>100</v>
-      </c>
-      <c r="O59" s="3">
-        <v>6900</v>
-      </c>
-      <c r="P59" s="3">
-        <v>6800</v>
       </c>
       <c r="Q59" s="3">
         <v>6900</v>
       </c>
       <c r="R59" s="3">
+        <v>6800</v>
+      </c>
+      <c r="S59" s="3">
         <v>6900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="U59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>200</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4286,50 +4559,56 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F60" s="3">
         <v>6700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4800</v>
       </c>
-      <c r="G60" s="3">
-        <v>3900</v>
-      </c>
-      <c r="H60" s="3">
-        <v>15300</v>
-      </c>
       <c r="I60" s="3">
-        <v>15000</v>
+        <v>2200</v>
       </c>
       <c r="J60" s="3">
         <v>15300</v>
       </c>
       <c r="K60" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L60" s="3">
+        <v>15300</v>
+      </c>
+      <c r="M60" s="3">
         <v>4200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1500</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -4363,74 +4642,80 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>55800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>57600</v>
+      </c>
+      <c r="F61" s="3">
         <v>66200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>66100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>75300</v>
       </c>
-      <c r="G61" s="3">
-        <v>68800</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>70300</v>
+      </c>
+      <c r="J61" s="3">
         <v>58800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>56400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>56500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>68700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>70700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>44900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>45100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>36700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>35400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>35500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>35000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>29000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>26800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>27200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>27300</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4440,50 +4725,56 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="E62" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="F62" s="3">
         <v>1400</v>
       </c>
       <c r="G62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K62" s="3">
         <v>900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
+        <v>900</v>
+      </c>
+      <c r="M62" s="3">
         <v>1000</v>
       </c>
-      <c r="I62" s="3">
-        <v>900</v>
-      </c>
-      <c r="J62" s="3">
-        <v>900</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="N62" s="3">
         <v>1000</v>
       </c>
-      <c r="L62" s="3">
-        <v>1000</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>500</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -4517,8 +4808,14 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4891,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4974,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,74 +5057,80 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>66500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>68900</v>
+      </c>
+      <c r="F66" s="3">
         <v>74500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>74000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>81800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>73700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>75200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>72500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>72800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>74200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>74200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>47200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>47200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>53500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>51900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>53700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>53700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>39800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>37700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>37400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>37600</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4825,8 +5140,14 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5175,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5254,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5337,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5035,17 +5370,17 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>11600</v>
       </c>
-      <c r="L70" s="3">
+      <c r="N70" s="3">
         <v>11600</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -5085,8 +5420,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,74 +5503,80 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-35700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-33600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-33300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-30400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-26000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-23300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-23000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-20000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-17800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-14800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-12700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-10800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-10000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-8600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-7000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-6000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-5400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-4600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-3100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-2800</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5239,8 +5586,14 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5669,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5752,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,74 +5835,80 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F76" s="3">
         <v>-3900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-1400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>9100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>11900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>6100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>8100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>9200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>10700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>11900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>11600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>12800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>13700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>14700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5547,8 +5918,14 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,131 +6001,143 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-4400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-600</v>
       </c>
       <c r="Q81" s="3">
         <v>-1000</v>
@@ -5757,34 +6146,40 @@
         <v>-600</v>
       </c>
       <c r="S81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="T81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U81" s="3">
         <v>-800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-200</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,34 +6207,36 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E83" s="3">
         <v>800</v>
       </c>
       <c r="F83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G83" s="3">
         <v>800</v>
       </c>
       <c r="H83" s="3">
+        <v>700</v>
+      </c>
+      <c r="I83" s="3">
+        <v>800</v>
+      </c>
+      <c r="J83" s="3">
         <v>500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
-      </c>
-      <c r="J83" s="3">
-        <v>400</v>
-      </c>
-      <c r="K83" s="3">
-        <v>400</v>
       </c>
       <c r="L83" s="3">
         <v>400</v>
@@ -5848,49 +6245,55 @@
         <v>400</v>
       </c>
       <c r="N83" s="3">
+        <v>400</v>
+      </c>
+      <c r="O83" s="3">
+        <v>400</v>
+      </c>
+      <c r="P83" s="3">
         <v>300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>600</v>
-      </c>
-      <c r="P83" s="3">
-        <v>600</v>
       </c>
       <c r="Q83" s="3">
         <v>600</v>
       </c>
       <c r="R83" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="S83" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="T83" s="3">
         <v>400</v>
       </c>
       <c r="U83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="V83" s="3">
         <v>400</v>
       </c>
       <c r="W83" s="3">
+        <v>400</v>
+      </c>
+      <c r="X83" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y83" s="3">
         <v>700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>100</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6369,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6452,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6535,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6618,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6701,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>500</v>
+      </c>
+      <c r="F89" s="3">
         <v>900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>700</v>
-      </c>
-      <c r="G89" s="3">
-        <v>200</v>
-      </c>
-      <c r="H89" s="3">
-        <v>600</v>
       </c>
       <c r="I89" s="3">
         <v>200</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K89" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
         <v>500</v>
-      </c>
-      <c r="M89" s="3">
-        <v>300</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-900</v>
       </c>
       <c r="O89" s="3">
         <v>300</v>
       </c>
       <c r="P89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>300</v>
+      </c>
+      <c r="R89" s="3">
         <v>400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>100</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-200</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-300</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,8 +6819,10 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6418,47 +6859,53 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-12800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-4900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-3400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-16700</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6981,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,8 +7064,14 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6620,76 +7079,82 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>10300</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
         <v>200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-6000</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-33100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
       </c>
       <c r="P94" s="3">
         <v>-100</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-12700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-4900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>1200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-16600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>100</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +7182,10 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6731,23 +7198,23 @@
       <c r="F96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>500</v>
-      </c>
-      <c r="K96" s="3">
-        <v>300</v>
-      </c>
-      <c r="L96" s="3">
-        <v>300</v>
       </c>
       <c r="M96" s="3">
         <v>300</v>
@@ -6756,25 +7223,25 @@
         <v>300</v>
       </c>
       <c r="O96" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="P96" s="3">
-        <v>-400</v>
+        <v>300</v>
       </c>
       <c r="Q96" s="3">
         <v>-300</v>
       </c>
       <c r="R96" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="S96" s="3">
         <v>-300</v>
       </c>
       <c r="T96" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="U96" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="V96" s="3">
         <v>0</v>
@@ -6794,8 +7261,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7344,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7427,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,85 +7510,97 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-9400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>4400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>34800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>6900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>1700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>12300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>17600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>700</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7140,11 +7637,11 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7179,81 +7676,93 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>2200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-6000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-3600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>13500</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>-400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA102" s="3" t="s">
+      <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
